--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -1,65 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Compte chefrayons kibo\Documents\EPICERIE K2\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{7BE6A8B4-A296-0D49-9608-AE7DBFAABC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Feuil1" sheetId="12" r:id="rId1"/>
+    <sheet sheetId="1" name="Export_Dlv" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>andrana</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Code barre</t>
+  </si>
+  <si>
+    <t>Code article</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Dlv</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>Prix (Ar)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>50025543</t>
+  </si>
+  <si>
+    <t>⚠️ HORS BASE</t>
+  </si>
+  <si>
+    <t>19/07/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="# ##0 &quot;Ar&quot;"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1e2f6b"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -74,8 +88,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -94,7 +117,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -104,44 +127,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -169,31 +192,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -221,23 +227,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -249,136 +238,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -400,41 +433,63 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8ABA10-F1E8-0847-A432-E7FF8B9EC0FE}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1234</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1">
-        <v>4321</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<SyracuseOfficeCustomData>{"createMode":"plain_doc","forceRefresh":"0"}</SyracuseOfficeCustomData>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3494333-1A28-40BE-99B3-ACD1F7E4A8DF}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8711" uniqueCount="4415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8719" uniqueCount="4418">
   <si>
     <t>Code barre</t>
   </si>
@@ -13256,6 +13256,15 @@
   </si>
   <si>
     <t>SORBET MANGUE PASSION 125ML</t>
+  </si>
+  <si>
+    <t>9661234100259</t>
+  </si>
+  <si>
+    <t>PAPIER HYGIENIQUE DOUCY ECO P12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCIETE DE PRODUCTION D'ARTICLES </t>
   </si>
 </sst>
 </file>
@@ -13632,7 +13641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2177"/>
+  <dimension ref="A1:E2179"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -50644,6 +50653,40 @@
         <v>3362</v>
       </c>
     </row>
+    <row r="2178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2178" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B2178">
+        <v>50042318</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>4416</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2178" t="s">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2179" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2179">
+        <v>50042319</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2179" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2179" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8719" uniqueCount="4418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8711" uniqueCount="4415">
   <si>
     <t>Code barre</t>
   </si>
@@ -13256,15 +13256,6 @@
   </si>
   <si>
     <t>SORBET MANGUE PASSION 125ML</t>
-  </si>
-  <si>
-    <t>9661234100259</t>
-  </si>
-  <si>
-    <t>PAPIER HYGIENIQUE DOUCY ECO P12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOCIETE DE PRODUCTION D'ARTICLES </t>
   </si>
 </sst>
 </file>
@@ -13641,7 +13632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2179"/>
+  <dimension ref="A1:E2177"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -50653,40 +50644,6 @@
         <v>3362</v>
       </c>
     </row>
-    <row r="2178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2178" t="s">
-        <v>4415</v>
-      </c>
-      <c r="B2178">
-        <v>50042318</v>
-      </c>
-      <c r="C2178" t="s">
-        <v>4416</v>
-      </c>
-      <c r="D2178" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2178" t="s">
-        <v>4417</v>
-      </c>
-    </row>
-    <row r="2179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2179" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2179">
-        <v>50042319</v>
-      </c>
-      <c r="C2179" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2179" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2179" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8719" uniqueCount="4418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8721" uniqueCount="4420">
   <si>
     <t>Code barre</t>
   </si>
@@ -13265,6 +13265,12 @@
   </si>
   <si>
     <t xml:space="preserve">SOCIETE DE PRODUCTION D'ARTICLES </t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>Andrana</t>
   </si>
 </sst>
 </file>
@@ -13641,7 +13647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2179"/>
+  <dimension ref="A1:E2180"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -50687,6 +50693,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2180">
+        <v>5321</v>
+      </c>
+      <c r="B2180">
+        <v>12345</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>4418</v>
+      </c>
+      <c r="D2180">
+        <v>30</v>
+      </c>
+      <c r="E2180" t="s">
+        <v>4419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8721" uniqueCount="4420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8801" uniqueCount="4462">
   <si>
     <t>Code barre</t>
   </si>
@@ -13271,6 +13271,132 @@
   </si>
   <si>
     <t>Andrana</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT ROUGE 100G</t>
+  </si>
+  <si>
+    <t>CODAL</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT VERT 100G</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT VERT 200G</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT ROUGE 200G</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT AU POIVRE SAUVAGE 100G</t>
+  </si>
+  <si>
+    <t>PUREE DE PIMENT AU COMBAVA 100G</t>
+  </si>
+  <si>
+    <t>RAVITOTO 420G</t>
+  </si>
+  <si>
+    <t>RAVITOTO COCO 420G</t>
+  </si>
+  <si>
+    <t>ACHARDS DE LEGUMES 130G</t>
+  </si>
+  <si>
+    <t>ACHARDS DE LEGUMES 400G</t>
+  </si>
+  <si>
+    <t>MOUTARDES  AROMATISEES À L'AIL 200G</t>
+  </si>
+  <si>
+    <t>MOUTARDES  AROMATISEES AU COMBAVA 200G</t>
+  </si>
+  <si>
+    <t>CITRONNELLE  FEUILLES BIO 50G</t>
+  </si>
+  <si>
+    <t>HIBISCUS FLEURS SECHEES BIO 50G</t>
+  </si>
+  <si>
+    <t>HIBISCUS FLEURS SECHEES BIO 100G</t>
+  </si>
+  <si>
+    <t>PICOLO CONFITURE  FRAISE 150G</t>
+  </si>
+  <si>
+    <t>PICOLO CONFITURE  TUTTI FRUITI 150G</t>
+  </si>
+  <si>
+    <t>PICOLO CONFITURE  PRUNE 150G</t>
+  </si>
+  <si>
+    <t>PICOLO CONFITURE  GOYAVE 150G</t>
+  </si>
+  <si>
+    <t>PICOLO COMPTOTE NATURE 150G</t>
+  </si>
+  <si>
+    <t>PICOLO COMPOTE POMMES BANANES 150G</t>
+  </si>
+  <si>
+    <t>PICOLO COMPOTE  POMMES FRAISES 150G</t>
+  </si>
+  <si>
+    <t>PICOLO COMPOTE POMMES EXOTIQUE 150G</t>
+  </si>
+  <si>
+    <t>CONFITURE  FRAISE 220G</t>
+  </si>
+  <si>
+    <t>CONFITURE  POKPOK 220G</t>
+  </si>
+  <si>
+    <t>CONFITURE  MURES 220G</t>
+  </si>
+  <si>
+    <t>CONFITURE  ORANGE 220G</t>
+  </si>
+  <si>
+    <t>SOAÏRA CHOCOLAT AU LAIT 45% AVEC PRALINE CACAHUETE 100G</t>
+  </si>
+  <si>
+    <t>SOAVA CHOCOLAT AU LAIT 33% AVEC PRALINE CAJOU 100G</t>
+  </si>
+  <si>
+    <t>MANIVA CHOCOLAT AU LAIT 33% GANACHE VANILLE 100G</t>
+  </si>
+  <si>
+    <t>VOANIA CHOCOLAT AU LAIT 45% AVE ÉCLATS DE NOIX DE COCO 75G</t>
+  </si>
+  <si>
+    <t>NOSIKO CHOCOLAT AU LAIT 33% 75G</t>
+  </si>
+  <si>
+    <t>CHAMPIGNON PARFUME 250GR SHIITAKE</t>
+  </si>
+  <si>
+    <t>YOPLAIT YAOURT A BOIRE VANILLE EN SACHET 70G</t>
+  </si>
+  <si>
+    <t>PANAGORA</t>
+  </si>
+  <si>
+    <t>YOPLAIT YAOURT A BOIRE FRASE EN SACHET 70G</t>
+  </si>
+  <si>
+    <t>BIBERON ZAZA COMPLET VERRE 120ML</t>
+  </si>
+  <si>
+    <t>BIBERON ZAZA COMPLET VERRE 240ML</t>
+  </si>
+  <si>
+    <t>TETINE ZAZA SILICONE ANTI-COLIQUE L (+6 MOIS)</t>
+  </si>
+  <si>
+    <t>TETINE ZAZA SILICONE ANTI-COLIQUE M (3-6 MOIS)</t>
+  </si>
+  <si>
+    <t>TETINE ZAZA SILICONE ANTI-COLIQUE S (0-3 MOIS)</t>
   </si>
 </sst>
 </file>
@@ -13647,7 +13773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2180"/>
+  <dimension ref="A1:E2220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -50710,6 +50836,686 @@
         <v>4419</v>
       </c>
     </row>
+    <row r="2181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2181">
+        <v>3760153582415</v>
+      </c>
+      <c r="B2181">
+        <v>50043101</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>4420</v>
+      </c>
+      <c r="D2181">
+        <v>24</v>
+      </c>
+      <c r="E2181" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2182">
+        <v>3760153582422</v>
+      </c>
+      <c r="B2182">
+        <v>50043102</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>4422</v>
+      </c>
+      <c r="D2182">
+        <v>24</v>
+      </c>
+      <c r="E2182" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2183">
+        <v>3760153584372</v>
+      </c>
+      <c r="B2183">
+        <v>71093221</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>4423</v>
+      </c>
+      <c r="D2183">
+        <v>12</v>
+      </c>
+      <c r="E2183" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2184">
+        <v>3760153584389</v>
+      </c>
+      <c r="B2184">
+        <v>71093222</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>4424</v>
+      </c>
+      <c r="D2184">
+        <v>12</v>
+      </c>
+      <c r="E2184" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2185">
+        <v>3076017392022</v>
+      </c>
+      <c r="B2185">
+        <v>71093223</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>4425</v>
+      </c>
+      <c r="D2185">
+        <v>24</v>
+      </c>
+      <c r="E2185" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2186">
+        <v>3760153599765</v>
+      </c>
+      <c r="B2186">
+        <v>71093224</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>4426</v>
+      </c>
+      <c r="D2186">
+        <v>24</v>
+      </c>
+      <c r="E2186" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2187">
+        <v>3760153581791</v>
+      </c>
+      <c r="B2187">
+        <v>71093225</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>4427</v>
+      </c>
+      <c r="D2187">
+        <v>12</v>
+      </c>
+      <c r="E2187" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2188">
+        <v>3760153599925</v>
+      </c>
+      <c r="B2188">
+        <v>71093226</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>4428</v>
+      </c>
+      <c r="D2188">
+        <v>12</v>
+      </c>
+      <c r="E2188" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2189">
+        <v>3760153580992</v>
+      </c>
+      <c r="B2189">
+        <v>71093227</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>4429</v>
+      </c>
+      <c r="D2189">
+        <v>24</v>
+      </c>
+      <c r="E2189" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2190">
+        <v>3760153583443</v>
+      </c>
+      <c r="B2190">
+        <v>71093228</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>4430</v>
+      </c>
+      <c r="D2190">
+        <v>24</v>
+      </c>
+      <c r="E2190" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2191">
+        <v>3760153581487</v>
+      </c>
+      <c r="B2191">
+        <v>71093229</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>4431</v>
+      </c>
+      <c r="D2191">
+        <v>12</v>
+      </c>
+      <c r="E2191" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2192">
+        <v>3760153581494</v>
+      </c>
+      <c r="B2192">
+        <v>71093230</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>4432</v>
+      </c>
+      <c r="D2192">
+        <v>12</v>
+      </c>
+      <c r="E2192" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2193">
+        <v>3760153590109</v>
+      </c>
+      <c r="B2193">
+        <v>71093231</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D2193">
+        <v>10</v>
+      </c>
+      <c r="E2193" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2194">
+        <v>3760153599048</v>
+      </c>
+      <c r="B2194">
+        <v>71093232</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D2194">
+        <v>12</v>
+      </c>
+      <c r="E2194" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2195">
+        <v>3760153599031</v>
+      </c>
+      <c r="B2195">
+        <v>71093233</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>4435</v>
+      </c>
+      <c r="D2195">
+        <v>12</v>
+      </c>
+      <c r="E2195" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2196">
+        <v>3760153599086</v>
+      </c>
+      <c r="B2196">
+        <v>71093234</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>4436</v>
+      </c>
+      <c r="D2196">
+        <v>24</v>
+      </c>
+      <c r="E2196" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2197">
+        <v>3760153599079</v>
+      </c>
+      <c r="B2197">
+        <v>71093235</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>4437</v>
+      </c>
+      <c r="D2197">
+        <v>24</v>
+      </c>
+      <c r="E2197" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2198">
+        <v>3760153599093</v>
+      </c>
+      <c r="B2198">
+        <v>71093236</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>4438</v>
+      </c>
+      <c r="D2198">
+        <v>24</v>
+      </c>
+      <c r="E2198" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2199">
+        <v>3760153599062</v>
+      </c>
+      <c r="B2199">
+        <v>71093237</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>4439</v>
+      </c>
+      <c r="D2199">
+        <v>24</v>
+      </c>
+      <c r="E2199" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2200">
+        <v>3760153599246</v>
+      </c>
+      <c r="B2200">
+        <v>71093238</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>4440</v>
+      </c>
+      <c r="D2200">
+        <v>24</v>
+      </c>
+      <c r="E2200" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2201">
+        <v>3760153599253</v>
+      </c>
+      <c r="B2201">
+        <v>71093239</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D2201">
+        <v>24</v>
+      </c>
+      <c r="E2201" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2202">
+        <v>3760153599260</v>
+      </c>
+      <c r="B2202">
+        <v>71093240</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>4442</v>
+      </c>
+      <c r="D2202">
+        <v>24</v>
+      </c>
+      <c r="E2202" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2203">
+        <v>3760153599277</v>
+      </c>
+      <c r="B2203">
+        <v>71093241</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>4443</v>
+      </c>
+      <c r="D2203">
+        <v>24</v>
+      </c>
+      <c r="E2203" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2204">
+        <v>3076017391025</v>
+      </c>
+      <c r="B2204">
+        <v>71093242</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>4444</v>
+      </c>
+      <c r="D2204">
+        <v>12</v>
+      </c>
+      <c r="E2204" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2205">
+        <v>3073017391100</v>
+      </c>
+      <c r="B2205">
+        <v>71093243</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>4445</v>
+      </c>
+      <c r="D2205">
+        <v>12</v>
+      </c>
+      <c r="E2205" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2206">
+        <v>3076017391049</v>
+      </c>
+      <c r="B2206">
+        <v>71093244</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>4446</v>
+      </c>
+      <c r="D2206">
+        <v>12</v>
+      </c>
+      <c r="E2206" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2207">
+        <v>3076017391070</v>
+      </c>
+      <c r="B2207">
+        <v>71093245</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>4447</v>
+      </c>
+      <c r="D2207">
+        <v>12</v>
+      </c>
+      <c r="E2207" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2208">
+        <v>619091605140</v>
+      </c>
+      <c r="B2208">
+        <v>71093246</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>4448</v>
+      </c>
+      <c r="D2208">
+        <v>10</v>
+      </c>
+      <c r="E2208" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2209">
+        <v>619091605157</v>
+      </c>
+      <c r="B2209">
+        <v>71093247</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>4449</v>
+      </c>
+      <c r="D2209">
+        <v>10</v>
+      </c>
+      <c r="E2209" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2210">
+        <v>619091605188</v>
+      </c>
+      <c r="B2210">
+        <v>71093248</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>4450</v>
+      </c>
+      <c r="D2210">
+        <v>10</v>
+      </c>
+      <c r="E2210" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2211">
+        <v>619091605126</v>
+      </c>
+      <c r="B2211">
+        <v>71093249</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>4451</v>
+      </c>
+      <c r="D2211">
+        <v>10</v>
+      </c>
+      <c r="E2211" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2212">
+        <v>619091605133</v>
+      </c>
+      <c r="B2212">
+        <v>71093250</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>4452</v>
+      </c>
+      <c r="D2212">
+        <v>10</v>
+      </c>
+      <c r="E2212" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2213">
+        <v>6091302492222</v>
+      </c>
+      <c r="B2213">
+        <v>71093251</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>4453</v>
+      </c>
+      <c r="D2213">
+        <v>12</v>
+      </c>
+      <c r="E2213" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2214">
+        <v>6091002019156</v>
+      </c>
+      <c r="B2214">
+        <v>75093252</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>4454</v>
+      </c>
+      <c r="D2214">
+        <v>10</v>
+      </c>
+      <c r="E2214" t="s">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2215">
+        <v>6091002019163</v>
+      </c>
+      <c r="B2215">
+        <v>75093253</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>4456</v>
+      </c>
+      <c r="D2215">
+        <v>10</v>
+      </c>
+      <c r="E2215" t="s">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2216">
+        <v>6900004304170</v>
+      </c>
+      <c r="B2216">
+        <v>74093254</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D2216">
+        <v>1</v>
+      </c>
+      <c r="E2216" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2217">
+        <v>6900004018954</v>
+      </c>
+      <c r="B2217">
+        <v>74093255</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>4458</v>
+      </c>
+      <c r="D2217">
+        <v>1</v>
+      </c>
+      <c r="E2217" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2218">
+        <v>6900004091094</v>
+      </c>
+      <c r="B2218">
+        <v>74093256</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>4459</v>
+      </c>
+      <c r="D2218">
+        <v>1</v>
+      </c>
+      <c r="E2218" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2219">
+        <v>6900004191817</v>
+      </c>
+      <c r="B2219">
+        <v>74093257</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D2219">
+        <v>1</v>
+      </c>
+      <c r="E2219" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2220">
+        <v>6900004193026</v>
+      </c>
+      <c r="B2220">
+        <v>74093258</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>4461</v>
+      </c>
+      <c r="D2220">
+        <v>1</v>
+      </c>
+      <c r="E2220" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/CADENCIER.xlsx
+++ b/CADENCIER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8801" uniqueCount="4462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8877" uniqueCount="4503">
   <si>
     <t>Code barre</t>
   </si>
@@ -13397,6 +13397,129 @@
   </si>
   <si>
     <t>TETINE ZAZA SILICONE ANTI-COLIQUE S (0-3 MOIS)</t>
+  </si>
+  <si>
+    <t>DIADERMINE SAVON DERMATOLOGIE 100G</t>
+  </si>
+  <si>
+    <t>DIADERMINE SAVON SURGRAS 100G</t>
+  </si>
+  <si>
+    <t>DIADERMINE PH 5 HYDRATANT PROTECTEUR DAY CREAM 50 ML</t>
+  </si>
+  <si>
+    <t>DIADERMINE PH 7 HYDRATANT MATIFIANT DAY CREAM 50 ML</t>
+  </si>
+  <si>
+    <t>MONT SAINT MICHEL BAR SOAP AMBREE 125G</t>
+  </si>
+  <si>
+    <t>MONT SAINT MICHEL BAR SOAP FRAICHEUR 125G</t>
+  </si>
+  <si>
+    <t>DENIVIT BLANCHEUR ET LUMIERE 50ML</t>
+  </si>
+  <si>
+    <t>DENIVIT BLANCHEUR SUBLIME 50ML</t>
+  </si>
+  <si>
+    <t>VADEMECUM FLUOR PLANTES 75ML</t>
+  </si>
+  <si>
+    <t>VADEMECUM PURETE ECALYPTUS 75ML</t>
+  </si>
+  <si>
+    <t>VADEMECUM BLANCHEUR ET PLANTES 75ML</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI PEARL POWDER &amp; MILK 175G</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI CREAM MILK 175G</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI ROSE MILK 175G</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI WHITE DIAMOND 175G</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI FRESH GREEN 175G</t>
+  </si>
+  <si>
+    <t>ROYAL LEXI AQUA FRESH 175G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROYAL LEXI ROMANTIC 175G </t>
+  </si>
+  <si>
+    <t>AYAM TERIYAKI SAUCE 210ML</t>
+  </si>
+  <si>
+    <t>SICE</t>
+  </si>
+  <si>
+    <t>AYAM SWEET SOUR SAUCE 210ML</t>
+  </si>
+  <si>
+    <t>AYAM YAKITORI SAUCE 210ML</t>
+  </si>
+  <si>
+    <t>AYAM PONZU SAUCE 210ML</t>
+  </si>
+  <si>
+    <t>AYAM CARAMELIZED SOYA SUCE 210ML</t>
+  </si>
+  <si>
+    <t>AYAM GREEN CURRY PASTE 100G</t>
+  </si>
+  <si>
+    <t>AYAM RED CURRY PASTE 100G</t>
+  </si>
+  <si>
+    <t>BISCUIT BAKERY BUTTER 66G</t>
+  </si>
+  <si>
+    <t>BRITA</t>
+  </si>
+  <si>
+    <t>BISCUITS COCONUT 66G</t>
+  </si>
+  <si>
+    <t>BISCUITS LU GALA EGG 100GR</t>
+  </si>
+  <si>
+    <t>BISCUITS NANKHATAI BAKERI 84G</t>
+  </si>
+  <si>
+    <t>TOPPER CUSTARD 125G</t>
+  </si>
+  <si>
+    <t>AZIMA</t>
+  </si>
+  <si>
+    <t>TOPPER CHOCOLATE 125G</t>
+  </si>
+  <si>
+    <t>TOPPER VANILLA 125G</t>
+  </si>
+  <si>
+    <t>TOPPER RASPBERRY 125G</t>
+  </si>
+  <si>
+    <t>EET SUM MOR CHOCOLATE CHIPS 200G</t>
+  </si>
+  <si>
+    <t>EET SUM MOR EXP 200G</t>
+  </si>
+  <si>
+    <t>EET SUM MOR 80G</t>
+  </si>
+  <si>
+    <t>TEA LATTE  GREEN MATCHA 240G</t>
+  </si>
+  <si>
+    <t>FARINE MULTIUSAGE FIONA 1KG</t>
   </si>
 </sst>
 </file>
@@ -13773,7 +13896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2220"/>
+  <dimension ref="A1:E2258"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -51516,6 +51639,652 @@
         <v>87</v>
       </c>
     </row>
+    <row r="2221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2221">
+        <v>3178040584679</v>
+      </c>
+      <c r="B2221">
+        <v>50042450</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>4462</v>
+      </c>
+      <c r="D2221">
+        <v>13500</v>
+      </c>
+      <c r="E2221" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2222">
+        <v>3178040585515</v>
+      </c>
+      <c r="B2222">
+        <v>50042451</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>4463</v>
+      </c>
+      <c r="D2222">
+        <v>13500</v>
+      </c>
+      <c r="E2222" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2223">
+        <v>3178044048528</v>
+      </c>
+      <c r="B2223">
+        <v>50042653</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>4464</v>
+      </c>
+      <c r="D2223">
+        <v>22500</v>
+      </c>
+      <c r="E2223" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2224">
+        <v>3178044048535</v>
+      </c>
+      <c r="B2224">
+        <v>50042654</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>4465</v>
+      </c>
+      <c r="D2224">
+        <v>22500</v>
+      </c>
+      <c r="E2224" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2225">
+        <v>3178040666283</v>
+      </c>
+      <c r="B2225">
+        <v>73093384</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>4466</v>
+      </c>
+      <c r="D2225">
+        <v>10900</v>
+      </c>
+      <c r="E2225" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2226">
+        <v>3178040666290</v>
+      </c>
+      <c r="B2226">
+        <v>73093385</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>4467</v>
+      </c>
+      <c r="D2226">
+        <v>10900</v>
+      </c>
+      <c r="E2226" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2227">
+        <v>4068881000140</v>
+      </c>
+      <c r="B2227">
+        <v>50048662</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>4468</v>
+      </c>
+      <c r="D2227">
+        <v>12500</v>
+      </c>
+      <c r="E2227" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2228">
+        <v>4068881000201</v>
+      </c>
+      <c r="B2228">
+        <v>50048663</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>4469</v>
+      </c>
+      <c r="D2228">
+        <v>12500</v>
+      </c>
+      <c r="E2228" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2229">
+        <v>4068883000216</v>
+      </c>
+      <c r="B2229">
+        <v>50042544</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>4470</v>
+      </c>
+      <c r="D2229">
+        <v>11500</v>
+      </c>
+      <c r="E2229" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2230">
+        <v>4068883000780</v>
+      </c>
+      <c r="B2230">
+        <v>50042546</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>4471</v>
+      </c>
+      <c r="D2230">
+        <v>11500</v>
+      </c>
+      <c r="E2230" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2231">
+        <v>4068883000230</v>
+      </c>
+      <c r="B2231">
+        <v>73093386</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>4472</v>
+      </c>
+      <c r="D2231">
+        <v>11500</v>
+      </c>
+      <c r="E2231" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2232">
+        <v>8997220606667</v>
+      </c>
+      <c r="B2232">
+        <v>73093387</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>4473</v>
+      </c>
+      <c r="D2232">
+        <v>3990</v>
+      </c>
+      <c r="E2232" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2233">
+        <v>8997220606698</v>
+      </c>
+      <c r="B2233">
+        <v>73093388</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>4474</v>
+      </c>
+      <c r="D2233">
+        <v>3990</v>
+      </c>
+      <c r="E2233" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2234">
+        <v>8997220606650</v>
+      </c>
+      <c r="B2234">
+        <v>73093389</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>4475</v>
+      </c>
+      <c r="D2234">
+        <v>3990</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2235">
+        <v>8997220606704</v>
+      </c>
+      <c r="B2235">
+        <v>73093390</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>4476</v>
+      </c>
+      <c r="D2235">
+        <v>3990</v>
+      </c>
+      <c r="E2235" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2236">
+        <v>8997220606674</v>
+      </c>
+      <c r="B2236">
+        <v>73093391</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>4477</v>
+      </c>
+      <c r="D2236">
+        <v>3990</v>
+      </c>
+      <c r="E2236" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2237">
+        <v>8997220606681</v>
+      </c>
+      <c r="B2237">
+        <v>73093392</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>4478</v>
+      </c>
+      <c r="D2237">
+        <v>3990</v>
+      </c>
+      <c r="E2237" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2238">
+        <v>8997220609965</v>
+      </c>
+      <c r="B2238">
+        <v>73093393</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>4479</v>
+      </c>
+      <c r="D2238">
+        <v>3990</v>
+      </c>
+      <c r="E2238" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2239">
+        <v>9556041611152</v>
+      </c>
+      <c r="B2239">
+        <v>71093394</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>4480</v>
+      </c>
+      <c r="D2239">
+        <v>12300</v>
+      </c>
+      <c r="E2239" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2240">
+        <v>9556041611121</v>
+      </c>
+      <c r="B2240">
+        <v>71093395</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D2240">
+        <v>13000</v>
+      </c>
+      <c r="E2240" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2241">
+        <v>9556041132411</v>
+      </c>
+      <c r="B2241">
+        <v>71093396</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>4483</v>
+      </c>
+      <c r="D2241">
+        <v>12300</v>
+      </c>
+      <c r="E2241" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2242">
+        <v>9556041132664</v>
+      </c>
+      <c r="B2242">
+        <v>71093397</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>4484</v>
+      </c>
+      <c r="D2242">
+        <v>10500</v>
+      </c>
+      <c r="E2242" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2243">
+        <v>9556041613620</v>
+      </c>
+      <c r="B2243">
+        <v>71093398</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>4485</v>
+      </c>
+      <c r="D2243">
+        <v>11500</v>
+      </c>
+      <c r="E2243" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2244">
+        <v>9556041780612</v>
+      </c>
+      <c r="B2244">
+        <v>71093399</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>4486</v>
+      </c>
+      <c r="D2244">
+        <v>8500</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2245">
+        <v>9556041780629</v>
+      </c>
+      <c r="B2245">
+        <v>71093400</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>4487</v>
+      </c>
+      <c r="D2245">
+        <v>8500</v>
+      </c>
+      <c r="E2245" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2246">
+        <v>8961003011740</v>
+      </c>
+      <c r="B2246">
+        <v>71093401</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>4488</v>
+      </c>
+      <c r="D2246">
+        <v>4000</v>
+      </c>
+      <c r="E2246" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2247">
+        <v>8961003011733</v>
+      </c>
+      <c r="B2247">
+        <v>71093402</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>4490</v>
+      </c>
+      <c r="D2247">
+        <v>4000</v>
+      </c>
+      <c r="E2247" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2248">
+        <v>8961003010521</v>
+      </c>
+      <c r="B2248">
+        <v>71093403</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>4491</v>
+      </c>
+      <c r="D2248">
+        <v>4000</v>
+      </c>
+      <c r="E2248" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2249">
+        <v>8961003011771</v>
+      </c>
+      <c r="B2249">
+        <v>71093404</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>4492</v>
+      </c>
+      <c r="D2249">
+        <v>4000</v>
+      </c>
+      <c r="E2249" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2250">
+        <v>6001056412940</v>
+      </c>
+      <c r="B2250">
+        <v>71093405</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>4493</v>
+      </c>
+      <c r="D2250">
+        <v>4500</v>
+      </c>
+      <c r="E2250" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2251">
+        <v>6001056412919</v>
+      </c>
+      <c r="B2251">
+        <v>71093406</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>4495</v>
+      </c>
+      <c r="D2251">
+        <v>4500</v>
+      </c>
+      <c r="E2251" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2252">
+        <v>6001056412933</v>
+      </c>
+      <c r="B2252">
+        <v>71093407</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>4496</v>
+      </c>
+      <c r="D2252">
+        <v>4500</v>
+      </c>
+      <c r="E2252" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2253">
+        <v>6001056412926</v>
+      </c>
+      <c r="B2253">
+        <v>71093408</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>4497</v>
+      </c>
+      <c r="D2253">
+        <v>4500</v>
+      </c>
+      <c r="E2253" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2254">
+        <v>6009704171294</v>
+      </c>
+      <c r="B2254">
+        <v>71093409</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>4498</v>
+      </c>
+      <c r="D2254">
+        <v>10500</v>
+      </c>
+      <c r="E2254" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2255">
+        <v>6001056201001</v>
+      </c>
+      <c r="B2255">
+        <v>71093410</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>4499</v>
+      </c>
+      <c r="D2255">
+        <v>10500</v>
+      </c>
+      <c r="E2255" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2256">
+        <v>6009704171874</v>
+      </c>
+      <c r="B2256">
+        <v>71093411</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D2256">
+        <v>4690</v>
+      </c>
+      <c r="E2256" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2257">
+        <v>6009702443447</v>
+      </c>
+      <c r="B2257">
+        <v>71093412</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>4501</v>
+      </c>
+      <c r="D2257">
+        <v>28500</v>
+      </c>
+      <c r="E2257" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2258">
+        <v>6091303395027</v>
+      </c>
+      <c r="B2258">
+        <v>71093413</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>4502</v>
+      </c>
+      <c r="D2258">
+        <v>4900</v>
+      </c>
+      <c r="E2258" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
